--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -548,7 +548,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>72025.39999999999</v>
+        <v>72083.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19.04</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3782.846638655462</v>
+        <v>3781.949108079748</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1703018621253787</v>
+        <v>0.1697823275192678</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05252100840336135</v>
+        <v>0.05246589716684156</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>84.06037242507574</v>
+        <v>83.95646550385356</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>91.50599051540151</v>
+        <v>91.47481843903485</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>21.83250454098099</v>
+        <v>21.83163617599649</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82589.01641628005</v>
+        <v>82566.13696373151</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.1466651544632873</v>
+        <v>0.1454163785937301</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>25.71643765339055</v>
+        <v>25.71470092342155</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97281.33973532121</v>
+        <v>97251.69022187163</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.3506532380982432</v>
+        <v>0.349144854324321</v>
       </c>
     </row>
     <row r="15"/>
@@ -4203,7 +4203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4294,6 +4294,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>72083.95</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.169782327519</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>72083.95</v>
+        <v>71804.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19.06</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>3781.949108079748</v>
+        <v>3783.142781875659</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1697823275192678</v>
+        <v>0.1701617842722332</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05246589716684156</v>
+        <v>0.05268703898840885</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>83.95646550385356</v>
+        <v>84.03235685444663</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>91.47481843903485</v>
+        <v>91.49758584421278</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>21.83163617599649</v>
+        <v>21.83227041085502</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82566.13696373151</v>
+        <v>82594.59621678368</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.1454163785937301</v>
+        <v>0.1502776823422032</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>25.71470092342155</v>
+        <v>25.71596939313861</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97251.69022187163</v>
+        <v>97287.18398858768</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.349144854324321</v>
+        <v>0.3548982820410225</v>
       </c>
     </row>
     <row r="15"/>
@@ -4203,7 +4203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4327,6 +4327,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>71804.05</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.170161784272</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +588,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +615,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>71804.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +623,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>18.98</v>
       </c>
     </row>
@@ -612,7 +633,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.05303030303030303</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +641,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>3783.142781875659</v>
       </c>
     </row>
@@ -630,7 +651,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.1701617842722332</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +669,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>94.6969696969697</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +677,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>84.03235685444663</v>
       </c>
     </row>
@@ -666,7 +687,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>91.49758584421278</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +736,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>21.83227041085502</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>82594.59621678368</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.1502776823422032</v>
       </c>
     </row>
@@ -732,17 +752,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>25.71596939313861</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>97287.18398858768</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.3548982820410225</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +815,19 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.2786054145137018</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1214942364637701</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.1307670492629717</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.1325583604561</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,17 +840,17 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.07759431716467646</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1080915253215654</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1172577320818432</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -844,17 +863,17 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>-0.0007165207175156008</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.06185084990092271</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.07686014505386762</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -867,17 +886,17 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.01440465370458754</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1581127875943407</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1345377776146478</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -890,21 +909,20 @@
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.07648733754079695</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1737002886945639</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1647363539071169</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1040,16 +1058,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>34759.2</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>42.66</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1059,16 +1077,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>37728.55</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>31.51</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1078,16 +1096,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>38513.25</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>30.75</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1097,16 +1115,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>39363.65</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>29.67</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1116,16 +1134,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>41585.45</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>28.93</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1135,16 +1153,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>42383.85</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>26.25</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1154,16 +1172,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>42087</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>25.76</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1173,16 +1191,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>41782.35</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>22.55</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1192,16 +1210,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>42217.9</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>22.94</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1211,16 +1229,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>41097.25</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>22.13</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1230,16 +1248,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>40052.1</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>20.77</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1249,16 +1267,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>41115.4</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>21.02</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1268,16 +1286,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>42533.95</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>21.74</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1287,16 +1305,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>38981.8</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>19.65</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1306,16 +1324,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>36505.4</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>18.32</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1325,16 +1343,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>40906.15</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>20.31</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1344,16 +1362,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>43709.15</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>23.42</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1363,16 +1381,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>42385.45</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>21.82</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1382,16 +1400,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>42623.85</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>22.25</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1401,16 +1419,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>43687.9</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>25.42</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1420,16 +1438,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>42187.65</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>25.63</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1439,16 +1457,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>39199.3</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>25.4</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1458,16 +1476,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>37252.55</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>25.78</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1477,16 +1495,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>37797.75</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>25.7</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1496,16 +1514,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>39514.2</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>26.8</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1515,16 +1533,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>42049.3</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>28.11</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1534,16 +1552,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>43750.3</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>29.09</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1553,16 +1571,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>45287</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>29.14</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1572,16 +1590,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>44415.5</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>25.1</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1591,16 +1609,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>45036.65</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>24.72</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1610,16 +1628,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>44019.1</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>23.52</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1629,16 +1647,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>48020.4</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>23.24</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1648,16 +1666,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>53344.8</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>25.65</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1667,16 +1685,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>55299.25</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>24.78</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1686,16 +1704,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>58991.35</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>25.52</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1705,16 +1723,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>60624.3</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>22.43</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1724,16 +1742,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>64900.5</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>24.06</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1743,16 +1761,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>67527.64999999999</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>24.1</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1762,16 +1780,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>71523.45</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>25.63</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1781,16 +1799,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>74788.10000000001</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>26.44</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1800,16 +1818,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>75279.8</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>26.79</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1819,16 +1837,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>77095.14999999999</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>24.8</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1838,16 +1856,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>69911.75</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>23.2</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1857,16 +1875,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>70726.85000000001</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>22.58</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1876,16 +1894,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>67988.35000000001</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>24.9</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1895,16 +1913,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>63127.35</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>23.34</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1914,16 +1932,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>57063.05</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>20.37</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1933,16 +1951,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>63043.2</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>21.48</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1952,16 +1970,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>64508.85</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>21.91</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1971,16 +1989,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>66761.3</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>21.85</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1990,16 +2008,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>68998.2</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>22.11</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2009,16 +2027,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>67096.14999999999</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>21.47</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2028,16 +2046,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>65745.75</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>20.34</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2047,16 +2065,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>67845.14999999999</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>20.66</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2066,16 +2084,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>69824.75</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>20.66</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2085,16 +2103,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>69137.45</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>20.12</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2104,16 +2122,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>69364.5</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>20.18</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2123,16 +2141,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>67839.85000000001</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>19.37</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2142,16 +2160,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>69710.89999999999</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>19.49</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2161,16 +2179,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>60349.8</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>17.09</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2180,16 +2198,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>69643.89999999999</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>19.7</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2199,16 +2217,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>71073.64999999999</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>19.27</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2218,16 +2236,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>71629.45</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>18.67</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2237,16 +2255,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>73651.3</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>19.49</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2256,16 +2274,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>73759.7</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>19.5</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2367,13 +2385,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>19977.05</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>22.14</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2381,12 +2399,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2394,31 +2412,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>18756.6</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>22.02</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2426,12 +2444,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2439,31 +2457,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>20533.7</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>25.9</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2471,12 +2489,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2484,31 +2502,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>22908</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>30.52</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2516,12 +2534,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2529,28 +2547,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>21389.7</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>25.14</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2558,15 +2576,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2574,28 +2592,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>25119.45</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>27.19</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2603,15 +2621,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2619,28 +2637,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>26254.5</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>27.48</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2648,15 +2666,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2664,28 +2682,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>27558.9</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>31.62</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2693,15 +2711,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2709,28 +2727,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>30964.65</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>37.82</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2738,15 +2756,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2754,28 +2772,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>28545.25</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>34.65</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2783,15 +2801,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2799,28 +2817,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>28291.7</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>40.93</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2828,15 +2846,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2844,28 +2862,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>27286.5</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>38.72</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2873,15 +2891,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2889,28 +2907,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>28178.8</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>42.42</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2918,15 +2936,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2934,28 +2952,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>28281.9</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>45.45</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2963,15 +2981,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2979,28 +2997,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>27332.5</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>46</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3008,15 +3026,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3024,28 +3042,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>27520.3</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>38.28</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3053,15 +3071,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3069,28 +3087,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>28307.55</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>65.43000000000001</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3098,15 +3116,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3114,28 +3132,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>21116.25</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>56.53</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3143,15 +3161,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3159,28 +3177,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>25743.7</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>30.76</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3188,15 +3206,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3204,28 +3222,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>27034.25</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>35.64</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3233,15 +3251,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3249,28 +3267,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>32508.55</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>41.24</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3278,15 +3296,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3294,28 +3312,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>34176.25</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>42.54</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3323,15 +3341,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3339,28 +3357,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>38513.25</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>30.75</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3368,15 +3386,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3384,28 +3402,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>42383.85</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>26.25</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3413,15 +3431,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3429,25 +3447,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>42217.9</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>22.94</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3455,15 +3473,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3471,25 +3489,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>41115.4</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>21.02</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3497,15 +3515,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3513,25 +3531,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>36505.4</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>18.32</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3539,15 +3557,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3555,25 +3573,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>42385.45</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>21.82</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3581,15 +3599,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3597,25 +3615,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>42187.65</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>25.63</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3623,15 +3641,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3639,25 +3657,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>37797.75</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.7</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3665,15 +3683,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3681,25 +3699,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>43750.3</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>29.09</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3707,15 +3725,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3723,25 +3741,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>45036.65</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>24.72</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3749,15 +3767,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3765,22 +3783,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>53344.8</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>25.65</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3788,15 +3806,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3804,22 +3822,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>60624.3</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>22.43</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3827,15 +3845,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3843,22 +3861,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>71523.45</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>25.63</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3866,15 +3884,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3882,22 +3900,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>77095.14999999999</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>24.8</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3905,15 +3923,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3921,22 +3939,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>67988.35000000001</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>24.9</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3944,15 +3962,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3960,22 +3978,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>63043.2</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>21.48</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3983,15 +4001,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3999,22 +4017,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>68998.2</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>22.11</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4022,15 +4040,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4038,22 +4056,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>67845.14999999999</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>20.66</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4061,15 +4079,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4077,19 +4095,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>69364.5</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>20.18</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4097,15 +4115,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4113,19 +4131,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>60349.8</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>17.09</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4133,15 +4151,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4149,19 +4167,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>71629.45</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>18.67</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4169,15 +4187,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4185,10 +4203,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4265,30 +4283,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>72025.39999999999</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>19.04</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.0530303030303</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.170301862125</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4298,30 +4316,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>72083.95</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>19.06</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.0530303030303</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.169782327519</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4331,30 +4349,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>71804.05</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>18.98</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.0530303030303</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.170161784272</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4370,6 +4388,1258 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Next 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="n">
+        <v>1.0003</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Indices Market Capitalisation &amp; Weightage</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="n">
+        <v>0.3385</v>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Divi's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>0.0474</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>0.04019999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tata Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0.0388</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hindustan Aeronautics Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>0.0359</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adani Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>0.03240000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>0.0317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson International Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="n">
+        <v>0.0297</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Torrent Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>0.0293</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cummins India Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>0.0272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bharat Petroleum Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="n">
+        <v>0.0259</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Indian Hotels Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="n">
+        <v>0.0255</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>0.0248</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CG Power and Industrial Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="n">
+        <v>0.0247</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Britannia Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="n">
+        <v>0.0244</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tata Power Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="n">
+        <v>0.0228</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Varun Beverages Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="n">
+        <v>0.0216</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HDFC Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="n">
+        <v>0.0211</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pidilite Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="n">
+        <v>0.0206</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Indian Oil Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="n">
+        <v>0.0205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="n">
+        <v>0.0199</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Power Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="n">
+        <v>0.0193</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Solar Industries India Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="n">
+        <v>0.0193</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GAIL (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="n">
+        <v>0.0189</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vedanta Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="n">
+        <v>0.0186</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Adani Energy Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="n">
+        <v>0.0183</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>DLF Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="n">
+        <v>0.0175</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bank of Baroda</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E32" s="37" t="n">
+        <v>0.0174</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Jindal Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E33" s="37" t="n">
+        <v>0.0174</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>United Spirits Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="n">
+        <v>0.0173</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bosch Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="n">
+        <v>0.0171</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Canara Bank</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E36" s="37" t="n">
+        <v>0.0168</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LTM Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="n">
+        <v>0.0166</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Adani Green Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>REC Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E39" s="37" t="n">
+        <v>0.0159</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ABB India Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E40" s="37" t="n">
+        <v>0.0158</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Punjab National Bank</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E41" s="37" t="n">
+        <v>0.0155</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Union Bank of India</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="n">
+        <v>0.0144</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="n">
+        <v>0.0143</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Siemens Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lodha Developers Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="n">
+        <v>0.0131</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Muthoot Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E46" s="37" t="n">
+        <v>0.0126</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Hyundai Motor India Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E47" s="37" t="n">
+        <v>0.0124</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Shree Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="E48" s="37" t="n">
+        <v>0.0122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Zydus Lifesciences Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E49" s="37" t="n">
+        <v>0.0114</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E50" s="37" t="n">
+        <v>0.0113</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Siemens Energy India Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ENRIN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E51" s="37" t="n">
+        <v>0.0113</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ambuja Cements Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="E52" s="37" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E53" s="37" t="n">
+        <v>0.0074</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tata Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TATACAP</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E54" s="37" t="n">
+        <v>0.0073</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Indian Railway Finance Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E55" s="37" t="n">
+        <v>0.0066</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>71804.05</v>
+        <v>72462.39999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.98</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3783.142781875659</v>
+        <v>3781.962421711899</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1701617842722332</v>
+        <v>0.1702658139592761</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05268703898840885</v>
+        <v>0.05219206680584551</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.03235685444663</v>
+        <v>84.05316279185521</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.49758584421278</v>
+        <v>91.50382762543535</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83227041085502</v>
+        <v>21.83244428904622</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82594.59621678368</v>
+        <v>82569.48387529138</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1502776823422032</v>
+        <v>0.1394803908688007</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.71596939313861</v>
+        <v>25.71631714952101</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97287.18398858768</v>
+        <v>97258.14508431371</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3548982820410225</v>
+        <v>0.342187742668111</v>
       </c>
     </row>
     <row r="16">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4378,6 +4378,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>72462.39999999999</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.170265813959</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>72462.39999999999</v>
+        <v>71381.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.16</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3781.962421711899</v>
+        <v>3782.800741918389</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1702658139592761</v>
+        <v>0.1704393923317642</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05219206680584551</v>
+        <v>0.05299417064122946</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.05316279185521</v>
+        <v>84.08787846635283</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.50382762543535</v>
+        <v>91.51424232778463</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83244428904622</v>
+        <v>21.83273441289738</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82569.48387529138</v>
+        <v>82588.88393521533</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1394803908688007</v>
+        <v>0.1570076530417264</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.71631714952101</v>
+        <v>25.71689739722333</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97258.14508431371</v>
+        <v>97281.89855405549</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.342187742668111</v>
+        <v>0.3628456490314429</v>
       </c>
     </row>
     <row r="16">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4411,6 +4411,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>71381.45</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.170439392332</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>71381.45</v>
+        <v>71778.64999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.87</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3782.800741918389</v>
+        <v>3783.798102266737</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1704393923317642</v>
+        <v>0.1707040684001537</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05299417064122946</v>
+        <v>0.05271481286241434</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.08787846635283</v>
+        <v>84.14081368003075</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.51424232778463</v>
+        <v>91.530122891888</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83273441289738</v>
+        <v>21.83317680004026</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82588.88393521533</v>
+        <v>82612.33294244646</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1570076530417264</v>
+        <v>0.1509318292061284</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.71689739722333</v>
+        <v>25.71778217150909</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97281.89855405549</v>
+        <v>97310.89537506539</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3628456490314429</v>
+        <v>0.3557080744074372</v>
       </c>
     </row>
     <row r="16">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4444,6 +4444,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>71778.64999999999</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.1707040684</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>71778.64999999999</v>
+        <v>70309.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.97</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05303030303030303</v>
+        <v>0.03787878787878788</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3783.798102266737</v>
+        <v>3782.114039806348</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1707040684001537</v>
+        <v>0.1699242996945838</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05271481286241434</v>
+        <v>0.05379236148466918</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.6969696969697</v>
+        <v>96.21212121212122</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.14081368003075</v>
+        <v>83.98485993891676</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.530122891888</v>
+        <v>92.54394283015986</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83317680004026</v>
+        <v>21.83187347234666</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82612.33294244646</v>
+        <v>82570.63517503807</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1509318292061284</v>
+        <v>0.1743880297120315</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.71778217150909</v>
+        <v>25.7151755161219</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97310.89537506539</v>
+        <v>97257.72635560906</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3557080744074372</v>
+        <v>0.3832800170049433</v>
       </c>
     </row>
     <row r="16">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4477,6 +4477,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>70309.5</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.0378787878788</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.169924299695</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>70309.5</v>
+        <v>69460.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.59</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3782.114039806348</v>
+        <v>3783.235294117647</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1699242996945838</v>
+        <v>0.1706345066717583</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05379236148466918</v>
+        <v>0.05446623093681918</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.98485993891676</v>
+        <v>84.12690133435166</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.54394283015986</v>
+        <v>92.58655524879035</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83187347234666</v>
+        <v>21.83306053257994</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82570.63517503807</v>
+        <v>82599.60518546346</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1743880297120315</v>
+        <v>0.1891645170250511</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.7151755161219</v>
+        <v>25.71754963658845</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97257.72635560906</v>
+        <v>97295.54146336387</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.3832800170049433</v>
+        <v>0.4007379976355363</v>
       </c>
     </row>
     <row r="16">
@@ -4221,7 +4221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4510,6 +4510,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>69460.2</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.0378787878788</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.170634506672</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,9 +570,9 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>69460.2</v>
+        <v>69746.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.36</v>
+        <v>18.28</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.02985074626865672</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3783.235294117647</v>
+        <v>3815.478665207877</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1706345066717583</v>
+        <v>0.1618780299431093</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05446623093681918</v>
+        <v>0.05470459518599562</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.21212121212122</v>
+        <v>97.01492537313433</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.12690133435166</v>
+        <v>82.37560598862186</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.58655524879035</v>
+        <v>92.62312955778057</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83306053257994</v>
+        <v>21.76404228408538</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>82599.60518546346</v>
+        <v>83040.2390036099</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1891645170250511</v>
+        <v>0.1905931227617823</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.71754963658845</v>
+        <v>25.67931214183908</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97295.54146336387</v>
+        <v>97978.8676144006</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4007379976355363</v>
+        <v>0.4047763753741289</v>
       </c>
     </row>
     <row r="16">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.07759431716467646</v>
+        <v>0.07007204182647042</v>
       </c>
       <c r="D19" s="30" t="n">
         <v>0.1080915253215654</v>
@@ -849,7 +849,9 @@
       <c r="E19" s="30" t="n">
         <v>0.1172577320818432</v>
       </c>
-      <c r="F19" s="30" t="n"/>
+      <c r="F19" s="30" t="n">
+        <v>0.1177734882312362</v>
+      </c>
       <c r="G19" s="30" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -861,20 +863,20 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>-0.0007165207175156008</v>
+        <v>0.01870926604048156</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.06185084990092271</v>
+        <v>0.1094072496872148</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.07686014505386762</v>
       </c>
       <c r="F20" s="30" t="n"/>
       <c r="G20" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -884,10 +886,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.01440465370458754</v>
+        <v>0.008568339655140811</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.1581127875943407</v>
@@ -916,7 +918,7 @@
         <v>0.1737002886945639</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.1647363539071169</v>
+        <v>0.1504408833107055</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -937,7 +939,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -947,7 +949,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -970,7 +972,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2289,6 +2291,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>69746.95</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2305,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2405,7 +2426,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2450,7 +2471,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2495,7 +2516,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2540,7 +2561,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2559,7 +2580,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2585,7 +2609,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2630,7 +2654,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2675,7 +2699,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2720,7 +2744,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2765,7 +2789,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2810,7 +2834,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2855,7 +2879,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2900,7 +2924,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2945,7 +2969,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2990,7 +3014,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3035,7 +3059,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3080,7 +3104,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3125,7 +3149,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3170,7 +3194,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3215,7 +3239,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3260,7 +3284,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3305,7 +3329,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3350,7 +3374,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3395,7 +3419,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3440,7 +3464,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3455,7 +3479,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3482,7 +3509,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3524,7 +3551,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3566,7 +3593,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3608,7 +3635,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3650,7 +3677,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3692,7 +3719,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3734,7 +3761,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3776,7 +3803,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3787,7 +3814,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3815,7 +3845,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3854,7 +3884,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3893,7 +3923,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3932,7 +3962,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3971,7 +4001,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4010,7 +4040,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4049,7 +4079,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4088,14 +4118,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4124,7 +4157,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4160,7 +4193,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4196,7 +4229,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4207,6 +4240,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>69746.95</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4221,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4229,7 +4298,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4543,6 +4612,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>69746.95</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.0298507462687</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.161878029943</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4583,7 +4685,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4592,7 +4694,7 @@
         </is>
       </c>
       <c r="E2" s="26" t="n">
-        <v>1.0003</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -4612,7 +4714,7 @@
         </is>
       </c>
       <c r="E3" s="26" t="n">
-        <v>0.3385</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="4"/>
@@ -4663,7 +4765,7 @@
         </is>
       </c>
       <c r="E6" s="37" t="n">
-        <v>0.0474</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="7">
@@ -4686,7 +4788,7 @@
         </is>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.0395</v>
       </c>
     </row>
     <row r="8">
@@ -4695,12 +4797,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd.</t>
+          <t>Hindustan Aeronautics Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4709,7 +4811,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>0.0388</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="9">
@@ -4718,12 +4820,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd.</t>
+          <t>Tata Motors Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4732,7 +4834,7 @@
         </is>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.0359</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="10">
@@ -4755,7 +4857,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="11">
@@ -4764,21 +4866,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+          <t>Samvardhana Motherson International Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.0317</v>
+        <v>0.0295</v>
       </c>
     </row>
     <row r="12">
@@ -4787,21 +4889,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>0.0297</v>
+        <v>0.0289</v>
       </c>
     </row>
     <row r="13">
@@ -4810,21 +4912,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0.0293</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="14">
@@ -4833,21 +4935,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>Vedanta Aluminium Metal Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>0.0272</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="15">
@@ -4856,21 +4958,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E15" s="37" t="n">
-        <v>0.0259</v>
+        <v>0.0263</v>
       </c>
     </row>
     <row r="16">
@@ -4879,12 +4981,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4893,7 +4995,7 @@
         </is>
       </c>
       <c r="E16" s="37" t="n">
-        <v>0.0255</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="17">
@@ -4902,21 +5004,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Bharat Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E17" s="37" t="n">
-        <v>0.0248</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="18">
@@ -4925,17 +5027,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E18" s="37" t="n">
@@ -4948,12 +5050,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4962,7 +5064,7 @@
         </is>
       </c>
       <c r="E19" s="37" t="n">
-        <v>0.0244</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="20">
@@ -4971,21 +5073,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Power Co. Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E20" s="37" t="n">
-        <v>0.0228</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="21">
@@ -4994,12 +5096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5008,7 +5110,7 @@
         </is>
       </c>
       <c r="E21" s="37" t="n">
-        <v>0.0216</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="22">
@@ -5017,21 +5119,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>Indian Oil Corporation Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>0.0211</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="23">
@@ -5040,12 +5142,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Solar Industries India Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5054,7 +5156,7 @@
         </is>
       </c>
       <c r="E23" s="37" t="n">
-        <v>0.0206</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="24">
@@ -5063,21 +5165,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.0205</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="25">
@@ -5100,7 +5202,7 @@
         </is>
       </c>
       <c r="E25" s="37" t="n">
-        <v>0.0199</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="26">
@@ -5109,12 +5211,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5123,7 +5225,7 @@
         </is>
       </c>
       <c r="E26" s="37" t="n">
-        <v>0.0193</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="27">
@@ -5132,21 +5234,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Solar Industries India Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.0193</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="28">
@@ -5155,21 +5257,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.0189</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="29">
@@ -5178,17 +5280,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E29" s="37" t="n">
@@ -5201,21 +5303,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adani Energy Solutions Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="E30" s="37" t="n">
-        <v>0.0183</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="31">
@@ -5224,21 +5326,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Adani Energy Solutions Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E31" s="37" t="n">
-        <v>0.0175</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="32">
@@ -5247,21 +5349,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Polycab India Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E32" s="37" t="n">
-        <v>0.0174</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="33">
@@ -5270,21 +5372,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Wipro Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E33" s="37" t="n">
-        <v>0.0174</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="34">
@@ -5293,21 +5395,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E34" s="37" t="n">
-        <v>0.0173</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="35">
@@ -5316,21 +5418,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bosch Ltd.</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E35" s="37" t="n">
-        <v>0.0171</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="36">
@@ -5339,21 +5441,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E36" s="37" t="n">
-        <v>0.0168</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="37">
@@ -5362,21 +5464,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTM Ltd.</t>
+          <t>Bosch Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E37" s="37" t="n">
-        <v>0.0166</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="38">
@@ -5385,21 +5487,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E38" s="37" t="n">
-        <v>0.016</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="39">
@@ -5408,21 +5510,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>Hitachi Energy India Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E39" s="37" t="n">
-        <v>0.0159</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="40">
@@ -5431,21 +5533,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ABB India Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E40" s="37" t="n">
-        <v>0.0158</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="41">
@@ -5454,21 +5556,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>LTM Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E41" s="37" t="n">
-        <v>0.0155</v>
+        <v>0.0154</v>
       </c>
     </row>
     <row r="42">
@@ -5477,21 +5579,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>ABB India Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E42" s="37" t="n">
-        <v>0.0144</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="43">
@@ -5500,21 +5602,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Ltd.</t>
+          <t>Vodafone Idea Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E43" s="37" t="n">
-        <v>0.0143</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="44">
@@ -5523,17 +5625,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Siemens Ltd.</t>
+          <t>Godrej Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E44" s="37" t="n">
@@ -5546,21 +5648,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lodha Developers Ltd.</t>
+          <t>Siemens Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E45" s="37" t="n">
-        <v>0.0131</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="46">
@@ -5569,12 +5671,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Muthoot Finance Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5583,7 +5685,7 @@
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>0.0126</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="47">
@@ -5592,21 +5694,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hyundai Motor India Ltd.</t>
+          <t>Muthoot Finance Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E47" s="37" t="n">
-        <v>0.0124</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="48">
@@ -5615,21 +5717,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>Hyundai Motor India Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>0.0122</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="49">
@@ -5652,7 +5754,7 @@
         </is>
       </c>
       <c r="E49" s="37" t="n">
-        <v>0.0114</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="50">
@@ -5661,21 +5763,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Ltd.</t>
+          <t>Siemens Energy India Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>ENRIN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E50" s="37" t="n">
-        <v>0.0113</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="51">
@@ -5684,21 +5786,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Siemens Energy India Ltd.</t>
+          <t>Hindustan Zinc Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E51" s="37" t="n">
-        <v>0.0113</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="52">
@@ -5721,7 +5823,7 @@
         </is>
       </c>
       <c r="E52" s="37" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="53">
@@ -5730,17 +5832,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>Tata Capital Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E53" s="37" t="n">
@@ -5753,12 +5855,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Capital Ltd.</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5776,17 +5878,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E55" s="37" t="n">

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>69746.95</v>
+        <v>68981.35000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.28</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02985074626865672</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3815.478665207877</v>
+        <v>3815.340154867257</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1618780299431093</v>
+        <v>0.1616263445664352</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05470459518599562</v>
+        <v>0.05530973451327434</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.01492537313433</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.37560598862186</v>
+        <v>82.32526891328705</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.62312955778057</v>
+        <v>93.13041649488163</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76404228408538</v>
+        <v>21.76290322798067</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83040.2390036099</v>
+        <v>83032.87857220488</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1905931227617823</v>
+        <v>0.2037003997776916</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67931214183908</v>
+        <v>25.67860023177363</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97978.8676144006</v>
+        <v>97972.59458506959</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4047763753741289</v>
+        <v>0.4202765614919044</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4645,6 +4645,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>68981.35000000001</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.161626344566</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68981.35000000001</v>
+        <v>69213.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.08</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3815.340154867257</v>
+        <v>3815.53197353914</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1616263445664352</v>
+        <v>0.1615854720565379</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05530973451327434</v>
+        <v>0.05512679162072767</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.32526891328705</v>
+        <v>82.31709441130759</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.13041649488163</v>
+        <v>93.1279641442878</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76290322798067</v>
+        <v>21.76271825067873</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83032.87857220488</v>
+        <v>83036.34731658848</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2037003997776916</v>
+        <v>0.1997088341057736</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67860023177363</v>
+        <v>25.67848462095992</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97972.59458506959</v>
+        <v>97977.07910330566</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4202765614919044</v>
+        <v>0.4155724708357178</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4678,6 +4678,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>69213.75</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.161585472057</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>69213.75</v>
+        <v>69973.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.14</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3815.53197353914</v>
+        <v>3815.359869138495</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1615854720565379</v>
+        <v>0.1620145380182048</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05512679162072767</v>
+        <v>0.05452562704471101</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.31709441130759</v>
+        <v>82.40290760364095</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.1279641442878</v>
+        <v>91.06415586318184</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76271825067873</v>
+        <v>21.76466008063096</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83036.34731658848</v>
+        <v>83040.01063707996</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1997088341057736</v>
+        <v>0.1867317383113936</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67848462095992</v>
+        <v>25.67969826468006</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97977.07910330566</v>
+        <v>97977.29021064576</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4155724708357178</v>
+        <v>0.4002016502006578</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4711,6 +4711,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>69973.7</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.162014538018</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>69973.7</v>
+        <v>69404</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.34</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3815.359869138495</v>
+        <v>3815.503023639362</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1620145380182048</v>
+        <v>0.1617995349476791</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05452562704471101</v>
+        <v>0.05497526113249038</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.40290760364095</v>
+        <v>82.35990698953582</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.06415586318184</v>
+        <v>93.14080791775626</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76466008063096</v>
+        <v>21.76368703816321</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83040.01063707996</v>
+        <v>83039.4136996525</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1867317383113936</v>
+        <v>0.1964643781288182</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67969826468006</v>
+        <v>25.67909011313772</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97977.29021064576</v>
+        <v>97978.64597098461</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4002016502006578</v>
+        <v>0.4117146846144979</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4744,6 +4744,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>69404</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.161799534948</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>69404</v>
+        <v>67614.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.19</v>
+        <v>17.72</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3815.503023639362</v>
+        <v>3815.716704288939</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1617995349476791</v>
+        <v>0.1619633066064106</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05497526113249038</v>
+        <v>0.05643340857787811</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.35990698953582</v>
+        <v>82.39266132128212</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.14080791775626</v>
+        <v>93.15063421728016</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76368703816321</v>
+        <v>21.76442822189873</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83039.4136996525</v>
+        <v>83046.89232559658</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1964643781288182</v>
+        <v>0.2282408703103118</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67909011313772</v>
+        <v>25.67955335297242</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97978.64597098461</v>
+        <v>97985.90068761588</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4117146846144979</v>
+        <v>0.4491847264657121</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4777,6 +4777,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>67614.5</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.161963306606</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>67614.5</v>
+        <v>68166.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.72</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3815.716704288939</v>
+        <v>3816.724524076148</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1619633066064106</v>
+        <v>0.1619466299703876</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05643340857787811</v>
+        <v>0.05599104143337066</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.39266132128212</v>
+        <v>82.38932599407751</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.15063421728016</v>
+        <v>93.14963361911877</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76442822189873</v>
+        <v>21.76435274820884</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83046.89232559658</v>
+        <v>83068.53888473278</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2282408703103118</v>
+        <v>0.2186087764954558</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67955335297242</v>
+        <v>25.67950618191624</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>97985.90068761588</v>
+        <v>98011.60101068475</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4491847264657121</v>
+        <v>0.4378222946201702</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4810,6 +4810,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>68166.7</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.16194662997</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68166.7</v>
+        <v>68351.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.86</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3816.724524076148</v>
+        <v>3816.398659966499</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1619466299703876</v>
+        <v>0.1623563320193946</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05599104143337066</v>
+        <v>0.05583472920156337</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.38932599407751</v>
+        <v>82.47126640387891</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.14963361911877</v>
+        <v>93.17421574205919</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76435274820884</v>
+        <v>21.76620694262492</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83068.53888473278</v>
+        <v>83068.52300838723</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2186087764954558</v>
+        <v>0.2153102703866507</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67950618191624</v>
+        <v>25.68066505342629</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98011.60101068475</v>
+        <v>98007.6556969446</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4378222946201702</v>
+        <v>0.4338729789741089</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4843,6 +4843,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>68351.7</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.162356332019</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68351.7</v>
+        <v>68927.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.91</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3816.398659966499</v>
+        <v>3816.608527131783</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1623563320193946</v>
+        <v>0.1621874407483723</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05583472920156337</v>
+        <v>0.05537098560354375</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.47126640387891</v>
+        <v>82.43748814967446</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.17421574205919</v>
+        <v>93.16408226579786</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76620694262492</v>
+        <v>21.76544258898692</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83068.52300838723</v>
+        <v>83070.17378192474</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2153102703866507</v>
+        <v>0.2051740082495526</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.68066505342629</v>
+        <v>25.68018733240254</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98007.6556969446</v>
+        <v>98011.22195118913</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4338729789741089</v>
+        <v>0.4219372830787675</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4876,6 +4876,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>68927.95</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.162187440748</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68927.95</v>
+        <v>68999.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.06</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3816.608527131783</v>
+        <v>3816.332964601771</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1621874407483723</v>
+        <v>0.1621130951170395</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05537098560354375</v>
+        <v>0.05530973451327434</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.43748814967446</v>
+        <v>82.4226190234079</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.16408226579786</v>
+        <v>93.15962152791789</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76544258898692</v>
+        <v>21.76510612190111</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83070.17378192474</v>
+        <v>83062.89197106702</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2051740082495526</v>
+        <v>0.2038222412555926</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.68018733240254</v>
+        <v>25.67997704047391</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98011.22195118913</v>
+        <v>98003.3429097772</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4219372830787675</v>
+        <v>0.4203527124155926</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4909,6 +4909,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>68999.3</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.162113095117</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68999.3</v>
+        <v>68671.60000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.08</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3816.332964601771</v>
+        <v>3821.457985531442</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1621130951170395</v>
+        <v>0.163353293465341</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05530973451327434</v>
+        <v>0.05564830272676684</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.4226190234079</v>
+        <v>82.67065869306821</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.15962152791789</v>
+        <v>93.23403342881598</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76510612190111</v>
+        <v>21.77071890528314</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83062.89197106702</v>
+        <v>83195.88761135458</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2038222412555926</v>
+        <v>0.2115035562205421</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67997704047391</v>
+        <v>25.68348503008768</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98003.3429097772</v>
+        <v>98148.35896450581</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4203527124155926</v>
+        <v>0.4292423500327034</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4942,6 +4942,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>68671.60000000001</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.163353293465</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68671.60000000001</v>
+        <v>68988.60000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.97</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3821.457985531442</v>
+        <v>3826.322795341098</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.163353293465341</v>
+        <v>0.1651979623899866</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05564830272676684</v>
+        <v>0.05546311702717693</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.67065869306821</v>
+        <v>83.03959247799733</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.23403342881598</v>
+        <v>93.34471356429472</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.77071890528314</v>
+        <v>21.77906734978782</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83195.88761135458</v>
+        <v>83333.74186176219</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2115035562205421</v>
+        <v>0.20793496116405</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.68348503008768</v>
+        <v>25.68870280790311</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98148.35896450581</v>
+        <v>98293.26913662253</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4292423500327034</v>
+        <v>0.4247755301110985</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4975,6 +4975,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>68988.60000000001</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.16519796239</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68988.60000000001</v>
+        <v>68695.85000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.03</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3826.322795341098</v>
+        <v>3831.335750139432</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1651979623899866</v>
+        <v>0.1661491345808102</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05546311702717693</v>
+        <v>0.05577244841048522</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.03959247799733</v>
+        <v>83.22982691616203</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.34471356429472</v>
+        <v>93.40178389574413</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.77906734978782</v>
+        <v>21.78337208336001</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83333.74186176219</v>
+        <v>83459.41222156647</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.20793496116405</v>
+        <v>0.2149119957256</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.68870280790311</v>
+        <v>25.69139326638572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98293.26913662253</v>
+        <v>98432.35349239508</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4247755301110985</v>
+        <v>0.432871905542985</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5008,6 +5008,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>68695.85000000001</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.166149134581</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68695.85000000001</v>
+        <v>67655.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.93</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3831.335750139432</v>
+        <v>3833.161473087819</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1661491345808102</v>
+        <v>0.1645106140726365</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05577244841048522</v>
+        <v>0.056657223796034</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>83.22982691616203</v>
+        <v>82.90212281452729</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.40178389574413</v>
+        <v>93.30347266525371</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.78337208336001</v>
+        <v>21.77595660768873</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83459.41222156647</v>
+        <v>83470.75790822456</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2149119957256</v>
+        <v>0.2337652468945457</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.69139326638572</v>
+        <v>25.68675859409117</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98432.35349239508</v>
+        <v>98461.49341137771</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.432871905542985</v>
+        <v>0.4553404302601232</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5041,6 +5041,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>67655.3</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.164510614073</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>67655.3</v>
+        <v>67354.14999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.65</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3833.161473087819</v>
+        <v>3855.417859187178</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1645106140726365</v>
+        <v>0.1712720818651017</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.056657223796034</v>
+        <v>0.05724098454493418</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.90212281452729</v>
+        <v>84.25441637302033</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.30347266525371</v>
+        <v>93.70916073280162</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.77595660768873</v>
+        <v>21.80655707906949</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>83470.75790822456</v>
+        <v>84073.38961002909</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2337652468945457</v>
+        <v>0.2482287967412415</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.68675859409117</v>
+        <v>25.70706066644497</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>98461.49341137771</v>
+        <v>99111.46080062019</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4553404302601232</v>
+        <v>0.4714974623036621</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5074,6 +5074,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>67354.14999999999</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.171272081865</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>67354.14999999999</v>
+        <v>65828.60000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.47</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3855.417859187178</v>
+        <v>3856.391329818395</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1712720818651017</v>
+        <v>0.1702300852427303</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05724098454493418</v>
+        <v>0.05858230814294083</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.25441637302033</v>
+        <v>84.04601704854606</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.70916073280162</v>
+        <v>94.69141705486231</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.80655707906949</v>
+        <v>21.80184130006996</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>84073.38961002909</v>
+        <v>84076.43176366639</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2482287967412415</v>
+        <v>0.2772021851241919</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.70706066644497</v>
+        <v>25.70352383219532</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>99111.46080062019</v>
+        <v>99122.84645225854</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4714974623036621</v>
+        <v>0.5057717534970898</v>
       </c>
     </row>
     <row r="16">
@@ -4290,13 +4290,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -5107,6 +5107,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>65828.60000000001</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.170230085243</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>65828.60000000001</v>
+        <v>66477.14999999999</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.07</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3856.391329818395</v>
+        <v>3862.704822777454</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1702300852427303</v>
+        <v>0.1723578890831987</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05858230814294083</v>
+        <v>0.05810575246949447</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.25373134328358</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.04601704854606</v>
+        <v>84.47157781663974</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>94.69141705486231</v>
+        <v>93.77430916588744</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.80184130006996</v>
+        <v>21.81147113230796</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>84076.43176366639</v>
+        <v>84251.27473463719</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2772021851241919</v>
+        <v>0.2673719426094108</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.70352383219532</v>
+        <v>25.71074620637383</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>99122.84645225854</v>
+        <v>99313.02336856733</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5057717534970898</v>
+        <v>0.4939422548735519</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5140,6 +5140,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>66477.14999999999</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.172357889083</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>66477.14999999999</v>
+        <v>67343.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.21</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3862.704822777454</v>
+        <v>3906.261600928075</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1723578890831987</v>
+        <v>0.1851406077038356</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05810575246949447</v>
+        <v>0.0580046403712297</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>84.47157781663974</v>
+        <v>87.02812154076712</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.77430916588744</v>
+        <v>94.54127228312565</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.81147113230796</v>
+        <v>21.83849577421737</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>84251.27473463719</v>
+        <v>85306.87746485532</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2673719426094108</v>
+        <v>0.2667340936320981</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.71074620637383</v>
+        <v>25.75413440557759</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>99313.02336856733</v>
+        <v>100602.3862936483</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4939422548735519</v>
+        <v>0.4938593042678421</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5173,6 +5173,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>67343.95</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.185140607704</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>67343.95</v>
+        <v>67303.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.24</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3906.261600928075</v>
+        <v>3908.461091753775</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1851406077038356</v>
+        <v>0.16252285453542</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0580046403712297</v>
+        <v>0.05807200929152149</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>87.02812154076712</v>
+        <v>82.504570907084</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>94.54127228312565</v>
+        <v>93.18420709302072</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.83849577421737</v>
+        <v>21.76696057595458</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>85306.87746485532</v>
+        <v>85075.31849685682</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2667340936320981</v>
+        <v>0.2640511368150165</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.75413440557759</v>
+        <v>25.68113607425733</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100602.3862936483</v>
+        <v>100373.7211382691</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4938593042678421</v>
+        <v>0.4913551727210994</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5206,6 +5206,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>67303.7</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.162522854535</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>67303.7</v>
+        <v>68121.60000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.22</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3908.461091753775</v>
+        <v>3908.29604130809</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.16252285453542</v>
+        <v>0.160718316273875</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05807200929152149</v>
+        <v>0.05737234652897304</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.504570907084</v>
+        <v>82.14366325477501</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.18420709302072</v>
+        <v>93.07593479732802</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.76696057595458</v>
+        <v>21.75879375136519</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>85075.31849685682</v>
+        <v>85039.80748209979</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2640511368150165</v>
+        <v>0.2483530551557771</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.68113607425733</v>
+        <v>25.67603180888896</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100373.7211382691</v>
+        <v>100349.5334751813</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4913551727210994</v>
+        <v>0.4730941944285116</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5239,6 +5239,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>68121.60000000001</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.160718316274</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-next-50.xlsx
+++ b/docs/downloads/indices/nifty-next-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>68121.60000000001</v>
+        <v>67709.10000000001</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.43</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>3908.29604130809</v>
+        <v>3952.661996497374</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.160718316273875</v>
+        <v>0.1742498349029156</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05737234652897304</v>
+        <v>0.05837711617046118</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.14366325477501</v>
+        <v>84.84996698058312</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>93.07593479732802</v>
+        <v>93.88782591507045</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>21.75879375136519</v>
+        <v>21.82001257694952</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>85039.80748209979</v>
+        <v>86247.13447600309</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2483530551557771</v>
+        <v>0.2737894090455062</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>25.67603180888896</v>
+        <v>25.7171680110419</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100349.5334751813</v>
+        <v>101651.2726547833</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4730941944285116</v>
+        <v>0.501294104555861</v>
       </c>
     </row>
     <row r="16">
@@ -4290,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5272,6 +5272,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>67709.10000000001</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.174249834903</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5294,7 +5327,7 @@
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5312,7 +5345,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5321,7 +5354,7 @@
         </is>
       </c>
       <c r="E2" s="26" t="n">
-        <v>0.9998999999999999</v>
+        <v>1.0005</v>
       </c>
     </row>
     <row r="3">
@@ -5341,7 +5374,7 @@
         </is>
       </c>
       <c r="E3" s="26" t="n">
-        <v>0.3373</v>
+        <v>0.3387</v>
       </c>
     </row>
     <row r="4"/>
@@ -5392,7 +5425,7 @@
         </is>
       </c>
       <c r="E6" s="37" t="n">
-        <v>0.0484</v>
+        <v>0.0524</v>
       </c>
     </row>
     <row r="7">
@@ -5415,7 +5448,7 @@
         </is>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.0395</v>
+        <v>0.0416</v>
       </c>
     </row>
     <row r="8">
@@ -5438,7 +5471,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>0.0363</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="9">
@@ -5461,7 +5494,7 @@
         </is>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.0361</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="10">
@@ -5484,7 +5517,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>0.0348</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="11">
@@ -5507,7 +5540,7 @@
         </is>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.0295</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="12">
@@ -5516,21 +5549,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>0.0289</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="13">
@@ -5539,21 +5572,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0.0288</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="14">
@@ -5576,7 +5609,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>0.0287</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="15">
@@ -5599,7 +5632,7 @@
         </is>
       </c>
       <c r="E15" s="37" t="n">
-        <v>0.0263</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="16">
@@ -5608,21 +5641,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E16" s="37" t="n">
-        <v>0.0251</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="17">
@@ -5645,7 +5678,7 @@
         </is>
       </c>
       <c r="E17" s="37" t="n">
-        <v>0.0249</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="18">
@@ -5654,21 +5687,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Power Co. Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E18" s="37" t="n">
-        <v>0.0247</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="19">
@@ -5677,12 +5710,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5691,7 +5724,7 @@
         </is>
       </c>
       <c r="E19" s="37" t="n">
-        <v>0.0242</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="20">
@@ -5700,21 +5733,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Wipro Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E20" s="37" t="n">
-        <v>0.024</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="21">
@@ -5723,12 +5756,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5737,7 +5770,7 @@
         </is>
       </c>
       <c r="E21" s="37" t="n">
-        <v>0.0233</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="22">
@@ -5746,21 +5779,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>0.0206</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="23">
@@ -5769,21 +5802,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Solar Industries India Ltd.</t>
+          <t>Indian Oil Corporation Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E23" s="37" t="n">
-        <v>0.0197</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="24">
@@ -5792,12 +5825,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5806,7 +5839,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.0194</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="25">
@@ -5815,12 +5848,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5829,7 +5862,7 @@
         </is>
       </c>
       <c r="E25" s="37" t="n">
-        <v>0.0191</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="26">
@@ -5838,21 +5871,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>Solar Industries India Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E26" s="37" t="n">
-        <v>0.0191</v>
+        <v>0.0193</v>
       </c>
     </row>
     <row r="27">
@@ -5861,21 +5894,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GAIL (India) Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.0188</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="28">
@@ -5884,21 +5917,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.0187</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="29">
@@ -5907,21 +5940,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E29" s="37" t="n">
-        <v>0.0186</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="30">
@@ -5930,21 +5963,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E30" s="37" t="n">
-        <v>0.0177</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="31">
@@ -5953,21 +5986,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adani Energy Solutions Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Realty</t>
         </is>
       </c>
       <c r="E31" s="37" t="n">
-        <v>0.0176</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="32">
@@ -5976,21 +6009,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>Adani Energy Solutions Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E32" s="37" t="n">
-        <v>0.0176</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="33">
@@ -5999,21 +6032,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wipro Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E33" s="37" t="n">
-        <v>0.0176</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="34">
@@ -6022,21 +6055,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E34" s="37" t="n">
-        <v>0.0175</v>
+        <v>0.0178</v>
       </c>
     </row>
     <row r="35">
@@ -6045,21 +6078,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E35" s="37" t="n">
-        <v>0.0175</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="36">
@@ -6068,21 +6101,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Polycab India Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E36" s="37" t="n">
-        <v>0.0172</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="37">
@@ -6105,7 +6138,7 @@
         </is>
       </c>
       <c r="E37" s="37" t="n">
-        <v>0.0167</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="38">
@@ -6128,7 +6161,7 @@
         </is>
       </c>
       <c r="E38" s="37" t="n">
-        <v>0.0164</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="39">
@@ -6137,21 +6170,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E39" s="37" t="n">
-        <v>0.016</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="40">
@@ -6160,21 +6193,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>LTM Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E40" s="37" t="n">
-        <v>0.0159</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="41">
@@ -6183,21 +6216,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTM Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E41" s="37" t="n">
-        <v>0.0154</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="42">
@@ -6206,12 +6239,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ABB India Ltd.</t>
+          <t>Hitachi Energy India Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6229,21 +6262,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>ABB India Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E43" s="37" t="n">
-        <v>0.0146</v>
+        <v>0.0142</v>
       </c>
     </row>
     <row r="44">
@@ -6266,7 +6299,7 @@
         </is>
       </c>
       <c r="E44" s="37" t="n">
-        <v>0.014</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="45">
@@ -6275,21 +6308,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Siemens Ltd.</t>
+          <t>Vodafone Idea Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
       <c r="E45" s="37" t="n">
-        <v>0.0135</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="46">
@@ -6298,21 +6331,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>0.0135</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="47">
@@ -6321,21 +6354,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Muthoot Finance Ltd.</t>
+          <t>Siemens Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E47" s="37" t="n">
-        <v>0.012</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="48">
@@ -6358,7 +6391,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>0.0118</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="49">
@@ -6367,21 +6400,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Muthoot Finance Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E49" s="37" t="n">
-        <v>0.0118</v>
+        <v>0.0109</v>
       </c>
     </row>
     <row r="50">
@@ -6404,7 +6437,7 @@
         </is>
       </c>
       <c r="E50" s="37" t="n">
-        <v>0.0116</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="51">
@@ -6427,7 +6460,7 @@
         </is>
       </c>
       <c r="E51" s="37" t="n">
-        <v>0.0111</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="52">
@@ -6450,7 +6483,7 @@
         </is>
       </c>
       <c r="E52" s="37" t="n">
-        <v>0.0095</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="53">
@@ -6496,7 +6529,7 @@
         </is>
       </c>
       <c r="E54" s="37" t="n">
-        <v>0.0073</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="55">
@@ -6519,7 +6552,7 @@
         </is>
       </c>
       <c r="E55" s="37" t="n">
-        <v>0.0066</v>
+        <v>0.005500000000000001</v>
       </c>
     </row>
   </sheetData>
